--- a/ksoft_old/docs/records/Customer_Group_Records_v2.xlsx
+++ b/ksoft_old/docs/records/Customer_Group_Records_v2.xlsx
@@ -1373,13 +1373,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29A878ED-D8B9-4B6F-B26C-56243C61FA08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{807B4525-F81E-4A7E-94C5-EE0AC5053386}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6099A36-77D9-456A-80EF-FB1B2441A201}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC868AF0-9358-4C3F-8020-BF11554543A9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EFBF0FF-1F71-4A6E-898D-BE2A6B227895}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7EEF5D4-CA1E-4E95-BFCE-B38559740AA1}"/>
 </file>
--- a/ksoft_old/docs/records/Customer_Group_Records_v2.xlsx
+++ b/ksoft_old/docs/records/Customer_Group_Records_v2.xlsx
@@ -1373,13 +1373,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{807B4525-F81E-4A7E-94C5-EE0AC5053386}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D15258C0-CEEB-4499-83DF-75159E517F46}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC868AF0-9358-4C3F-8020-BF11554543A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C61B597-29B8-4A24-B773-AA6F52CB44D2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7EEF5D4-CA1E-4E95-BFCE-B38559740AA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900959BC-E90A-45D6-8D9C-75640C5E164A}"/>
 </file>
--- a/ksoft_old/docs/records/Customer_Group_Records_v2.xlsx
+++ b/ksoft_old/docs/records/Customer_Group_Records_v2.xlsx
@@ -1373,13 +1373,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D15258C0-CEEB-4499-83DF-75159E517F46}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29A878ED-D8B9-4B6F-B26C-56243C61FA08}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C61B597-29B8-4A24-B773-AA6F52CB44D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6099A36-77D9-456A-80EF-FB1B2441A201}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900959BC-E90A-45D6-8D9C-75640C5E164A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EFBF0FF-1F71-4A6E-898D-BE2A6B227895}"/>
 </file>